--- a/buckman/output/ingested_data/2024/2024_Table_2_output.xlsx
+++ b/buckman/output/ingested_data/2024/2024_Table_2_output.xlsx
@@ -591,9 +591,8 @@
       <c r="M2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N2" s="3">
-        <f>SUM(B2:M2)</f>
-        <v/>
+      <c r="N2" s="3" t="n">
+        <v>601.279624</v>
       </c>
       <c r="O2" s="2" t="n">
         <v>1</v>
@@ -639,9 +638,8 @@
       <c r="M3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="N3" s="5">
-        <f>SUM(B3:M3)</f>
-        <v/>
+      <c r="N3" s="5" t="n">
+        <v>0.009207</v>
       </c>
       <c r="O3" s="4" t="n">
         <v>2</v>
@@ -687,9 +685,8 @@
       <c r="M4" s="7" t="n">
         <v>0.052171</v>
       </c>
-      <c r="N4" s="7">
-        <f>SUM(B4:M4)</f>
-        <v/>
+      <c r="N4" s="7" t="n">
+        <v>56.227742</v>
       </c>
       <c r="O4" s="6" t="n">
         <v>3</v>
@@ -735,9 +732,8 @@
       <c r="M5" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N5" s="7">
-        <f>SUM(B5:M5)</f>
-        <v/>
+      <c r="N5" s="7" t="n">
+        <v>63.335233</v>
       </c>
       <c r="O5" s="6" t="n">
         <v>4</v>
@@ -783,9 +779,8 @@
       <c r="M6" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N6" s="7">
-        <f>SUM(B6:M6)</f>
-        <v/>
+      <c r="N6" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="O6" s="6" t="n">
         <v>5</v>
@@ -831,9 +826,8 @@
       <c r="M7" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N7" s="7">
-        <f>SUM(B7:M7)</f>
-        <v/>
+      <c r="N7" s="7" t="n">
+        <v>152.221835</v>
       </c>
       <c r="O7" s="6" t="n">
         <v>6</v>
@@ -879,9 +873,8 @@
       <c r="M8" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N8" s="7">
-        <f>SUM(B8:M8)</f>
-        <v/>
+      <c r="N8" s="7" t="n">
+        <v>1.00045</v>
       </c>
       <c r="O8" s="6" t="n">
         <v>7</v>
@@ -927,9 +920,8 @@
       <c r="M9" s="7" t="n">
         <v>47.502959</v>
       </c>
-      <c r="N9" s="7">
-        <f>SUM(B9:M9)</f>
-        <v/>
+      <c r="N9" s="7" t="n">
+        <v>111.46731</v>
       </c>
       <c r="O9" s="6" t="n">
         <v>8</v>
@@ -975,9 +967,8 @@
       <c r="M10" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N10" s="7">
-        <f>SUM(B10:M10)</f>
-        <v/>
+      <c r="N10" s="7" t="n">
+        <v>0.524776</v>
       </c>
       <c r="O10" s="6" t="n">
         <v>9</v>
@@ -1023,9 +1014,8 @@
       <c r="M11" s="7" t="n">
         <v>12.235564</v>
       </c>
-      <c r="N11" s="7">
-        <f>SUM(B11:M11)</f>
-        <v/>
+      <c r="N11" s="7" t="n">
+        <v>151.417792</v>
       </c>
       <c r="O11" s="6" t="n">
         <v>10</v>
@@ -1071,9 +1061,8 @@
       <c r="M12" s="7" t="n">
         <v>2.547158</v>
       </c>
-      <c r="N12" s="7">
-        <f>SUM(B12:M12)</f>
-        <v/>
+      <c r="N12" s="7" t="n">
+        <v>13.619622</v>
       </c>
       <c r="O12" s="6" t="n">
         <v>11</v>
@@ -1119,9 +1108,8 @@
       <c r="M13" s="9" t="n">
         <v>1.304268</v>
       </c>
-      <c r="N13" s="9">
-        <f>SUM(B13:M13)</f>
-        <v/>
+      <c r="N13" s="9" t="n">
+        <v>9.801954</v>
       </c>
       <c r="O13" s="8" t="n">
         <v>12</v>
@@ -1167,9 +1155,8 @@
       <c r="M14" s="3" t="n">
         <v>2.043864</v>
       </c>
-      <c r="N14" s="3">
-        <f>SUM(B14:M14)</f>
-        <v/>
+      <c r="N14" s="3" t="n">
+        <v>212.018667</v>
       </c>
       <c r="O14" s="2" t="n">
         <v>13</v>
@@ -1196,78 +1183,61 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B15" s="11">
-        <f>SUM(B2:B14)</f>
-        <v/>
-      </c>
-      <c r="C15" s="11">
-        <f>SUM(C2:C14)</f>
-        <v/>
-      </c>
-      <c r="D15" s="11">
-        <f>SUM(D2:D14)</f>
-        <v/>
-      </c>
-      <c r="E15" s="11">
-        <f>SUM(E2:E14)</f>
-        <v/>
-      </c>
-      <c r="F15" s="11">
-        <f>SUM(F2:F14)</f>
-        <v/>
-      </c>
-      <c r="G15" s="11">
-        <f>SUM(G2:G14)</f>
-        <v/>
-      </c>
-      <c r="H15" s="11">
-        <f>SUM(H2:H14)</f>
-        <v/>
-      </c>
-      <c r="I15" s="11">
-        <f>SUM(I2:I14)</f>
-        <v/>
-      </c>
-      <c r="J15" s="11">
-        <f>SUM(J2:J14)</f>
-        <v/>
-      </c>
-      <c r="K15" s="11">
-        <f>SUM(K2:K14)</f>
-        <v/>
-      </c>
-      <c r="L15" s="11">
-        <f>SUM(L2:L14)</f>
-        <v/>
-      </c>
-      <c r="M15" s="11">
-        <f>SUM(M2:M14)</f>
-        <v/>
-      </c>
-      <c r="N15" s="11">
-        <f>SUM(B15:M15)</f>
-        <v/>
+      <c r="B15" s="11" t="n">
+        <v>19.379882</v>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>39.385812</v>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>13.094846</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>44.489334</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>88.653368</v>
+      </c>
+      <c r="G15" s="11" t="n">
+        <v>168.020351</v>
+      </c>
+      <c r="H15" s="11" t="n">
+        <v>302.043818</v>
+      </c>
+      <c r="I15" s="11" t="n">
+        <v>333.953874</v>
+      </c>
+      <c r="J15" s="11" t="n">
+        <v>141.594356</v>
+      </c>
+      <c r="K15" s="11" t="n">
+        <v>135.837165</v>
+      </c>
+      <c r="L15" s="11" t="n">
+        <v>20.785422</v>
+      </c>
+      <c r="M15" s="11" t="n">
+        <v>65.685984</v>
+      </c>
+      <c r="N15" s="11" t="n">
+        <v>1372.924212</v>
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="Q15" s="12">
-        <f>SUM(N11:N14)</f>
-        <v/>
-      </c>
-      <c r="R15" s="13">
-        <f>Q15/N15</f>
-        <v/>
-      </c>
-      <c r="S15" s="12">
-        <f>N2+N8+N9</f>
-        <v/>
-      </c>
-      <c r="T15" s="13">
-        <f>S15/N15</f>
-        <v/>
+      <c r="Q15" s="12" t="n">
+        <v>386.858035</v>
+      </c>
+      <c r="R15" s="13" t="n">
+        <v>0.2817766863011664</v>
+      </c>
+      <c r="S15" s="12" t="n">
+        <v>713.747384</v>
+      </c>
+      <c r="T15" s="13" t="n">
+        <v>0.5198738413683101</v>
       </c>
     </row>
   </sheetData>
